--- a/stage4_course_extraction/output/10_课程标准人工审查问题清单.xlsx
+++ b/stage4_course_extraction/output/10_课程标准人工审查问题清单.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人工审查问题" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'人工审查问题'!$A$1:$E$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'人工审查问题'!$A$1:$K$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -433,6 +433,12 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -461,6 +467,36 @@
           <t>审查状态</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>原问题编号</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>问题描述</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>本次处理动作</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>证据依据</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>当前状态</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>是否仍需研究者确认</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -488,6 +524,36 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CQ001</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>文本层实训与考核标题在页面渲染中不可见，不能作为已确认正向实践/考核证据</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>保留原问题，不自动关闭</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>PDF第13页</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>待研究者确认</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -515,6 +581,36 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CQ002</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>精确逐项学时对应未明示</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>保留原问题，不自动关闭</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>PT01—PT03与P01—P08</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>待研究者确认</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -542,6 +638,36 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CQ003</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>INERT INTO疑似拼写错误</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>保留原问题，不自动关闭</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>PT02</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>待研究者确认</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -569,6 +695,36 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CQ004</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>末尾只有不可见标题，未提供可读评分细则或比例</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>保留原问题，不自动关闭</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>课程考核</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>待研究者确认</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,6 +752,36 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CQ005</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>权限管理/DCL在总体目标，P08技术实践正文主要备份恢复及事务</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>保留原问题，不自动关闭</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>目标与项目</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>待研究者确认</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -623,6 +809,36 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CQ006</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>替代键/唯一键术语对照需审查</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>保留原问题，不自动关闭</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>待研究者确认</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -650,6 +866,36 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CQ007</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>分组聚会疑似分组聚合笔误</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>保留原问题，不自动关闭</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>待研究者确认</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -677,6 +923,36 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CQ008</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>索引分类与作疑似缺字</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>保留原问题，不自动关闭</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>待研究者确认</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -704,6 +980,36 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CQ009</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>DELETE可回滚与TRUNCATE不可逆表述缺少存储引擎/事务条件</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>保留原问题，不自动关闭</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>待研究者确认</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -731,6 +1037,36 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CQ010</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>多数仅要求完成操作，未规定交付文件形式</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>保留原问题，不自动关闭</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>学习成果</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>待研究者确认</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -750,12 +1086,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>共用规范化实体，出现记录分别保留；审查边界是否适当</t>
+          <t>审查新增CK060边界及行为接口；不关闭其他11项问题</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>待研究者审查</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CQ011</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>CREATE TABLE在P03库表与P07建表索引语境、WHERE在操作和查询语境出现</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>CK015保留P03；KO056迁移至新增CK060建表时定义索引；CK027共用实体，补充P04/P05应用语境；CK057新增两技术行为接口</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>PDF第5、7、8、11、12页；KO015/KO056/KO027/KO034；CTB001/CTB002</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>技术修订已落实，待研究者最终确认</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -785,9 +1151,39 @@
           <t>待研究者审查</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CQ012</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>部分标题编码异常，P02教室需求疑似教师需求</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>保留原问题，不自动关闭</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>课程定位/页眉</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>待研究者确认</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E13"/>
+  <autoFilter ref="A1:K13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>